--- a/backend/data/excel/432ade6bad5a_data.xlsx
+++ b/backend/data/excel/432ade6bad5a_data.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-25 16:48:15</t>
+          <t>2025-09-26 09:20:10</t>
         </is>
       </c>
     </row>
